--- a/astro-site/public/dl/restaurant-schedule-templates/06-employee-performance-review.xlsx
+++ b/astro-site/public/dl/restaurant-schedule-templates/06-employee-performance-review.xlsx
@@ -1577,7 +1577,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="C12:C21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid score" error="Type 1, 2, 3, 4, 5 or N/A." promptTitle="kitgp-v2c · Invalid score" prompt="1 = Unsatisfactory · 2 = Needs improvement · 3 = Meets expectations · 4 = Good · 5 = Excellent. Choose N/A when the competency does not apply to the position (a line cook does not wait tables): the average uses ONLY what was rated, so N/A does not penalize." type="list" errorStyle="stop">
+    <dataValidation sqref="C12:C21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid score" error="Type 1, 2, 3, 4, 5 or N/A." promptTitle="Score" prompt="1 = Unsatisfactory · 2 = Needs improvement · 3 = Meets expectations · 4 = Good · 5 = Excellent. Pick N/A when the competency does not apply to the position (a line cook does not wait tables): the average uses ONLY what was rated." type="list" errorStyle="stop">
       <formula1>"1,2,3,4,5,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2217,7 +2217,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="C12:C21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid score" error="Type 1, 2, 3, 4, 5 or N/A." promptTitle="kitgp-v2c · Invalid score" prompt="1 = Unsatisfactory · 2 = Needs improvement · 3 = Meets expectations · 4 = Good · 5 = Excellent. Choose N/A when the competency does not apply to the position (a line cook does not wait tables): the average uses ONLY what was rated, so N/A does not penalize." type="list" errorStyle="stop">
+    <dataValidation sqref="C12:C21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid score" error="Type 1, 2, 3, 4, 5 or N/A." promptTitle="Score" prompt="1 = Unsatisfactory · 2 = Needs improvement · 3 = Meets expectations · 4 = Good · 5 = Excellent. Pick N/A when the competency does not apply to the position (a line cook does not wait tables): the average uses ONLY what was rated." type="list" errorStyle="stop">
       <formula1>"1,2,3,4,5,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2780,7 +2780,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="64" t="inlineStr">
         <is>
-          <t>▸ The tab holds 30 employees, the same as the staff directory (file 07 (Employee Directory &amp; Expiry Tracker)) and the schedule (file 01 (Restaurant Schedule Template: Weekly &amp; Monthly Staff Rota)).</t>
+          <t>▸ The tab holds 30 employees, the same as the staff directory (file 07 "Employee Directory &amp; Expiry Tracker") and the schedule (file 01 "Restaurant Schedule Template").</t>
         </is>
       </c>
     </row>
